--- a/REIT_Pairs_Analytics_2026-07-11.xlsx
+++ b/REIT_Pairs_Analytics_2026-07-11.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
-    <t xml:space="preserve">Report Created: July 11, 2026 06:27 AM   |   Last Data Point in Analysis: July 10, 2026</t>
+    <t xml:space="preserve">Report Created: July 11, 2026 07:26 AM   |   Last Data Point in Analysis: July 10, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Recommendation Changes  |  Week of: July 11, 2026</t>

--- a/REIT_Pairs_Analytics_2026-07-11.xlsx
+++ b/REIT_Pairs_Analytics_2026-07-11.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
-    <t xml:space="preserve">Report Created: July 11, 2026 07:26 AM   |   Last Data Point in Analysis: July 10, 2026</t>
+    <t xml:space="preserve">Report Created: July 11, 2026 01:10 PM   |   Last Data Point in Analysis: July 10, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Recommendation Changes  |  Week of: July 11, 2026</t>
